--- a/reports/data_quality_report.xlsx
+++ b/reports/data_quality_report.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -845,7 +845,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>COST_OVERRUN_PCT</t>
+          <t>PROJECT_ID</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -854,19 +854,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="E21" t="n">
-        <v>1022</v>
+        <v>2073</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>PROGRESS_GAP</t>
+          <t>COST_OVERRUN_PCT</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -875,33 +875,54 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>6086</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>PROGRESS_GAP</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>float64</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>4</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E23" t="n">
+        <v>6238</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>SCHEDULE_CHANGE_DAYS</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>float64</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>float64</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
         <v>1382</v>
       </c>
-      <c r="D23" t="n">
+      <c r="D24" t="n">
         <v>18.2</v>
       </c>
-      <c r="E23" t="n">
+      <c r="E24" t="n">
         <v>249</v>
       </c>
     </row>
